--- a/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0002T0006Z000C1N21_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0002T0006Z000C1N21_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>45.01722748441805</v>
+        <v>7.315299466217933</v>
       </c>
       <c r="D2" t="n">
-        <v>43.59101534250107</v>
+        <v>7.083539993156425</v>
       </c>
       <c r="E2" t="n">
-        <v>12.9434067117825</v>
+        <v>2.103303590664656</v>
       </c>
       <c r="F2" t="n">
-        <v>16.94291744149149</v>
+        <v>2.753224084242368</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>19.86180377767318</v>
+        <v>3.227543113871893</v>
       </c>
       <c r="D3" t="n">
-        <v>21.97463118640027</v>
+        <v>3.570877567790043</v>
       </c>
       <c r="E3" t="n">
-        <v>12.9434067117825</v>
+        <v>2.103303590664656</v>
       </c>
       <c r="F3" t="n">
-        <v>16.94291744149149</v>
+        <v>2.753224084242368</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>38.78805885845996</v>
+        <v>6.303059564499744</v>
       </c>
       <c r="D4" t="n">
-        <v>36.33087580935854</v>
+        <v>5.903767319020763</v>
       </c>
       <c r="E4" t="n">
-        <v>12.9434067117825</v>
+        <v>2.103303590664656</v>
       </c>
       <c r="F4" t="n">
-        <v>16.94291744149149</v>
+        <v>2.753224084242368</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>48.46257281657216</v>
+        <v>7.875168082692976</v>
       </c>
       <c r="D5" t="n">
-        <v>48.57096711952909</v>
+        <v>7.892782156923477</v>
       </c>
       <c r="E5" t="n">
-        <v>12.9434067117825</v>
+        <v>2.103303590664656</v>
       </c>
       <c r="F5" t="n">
-        <v>16.94291744149149</v>
+        <v>2.753224084242368</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>50.28944750502152</v>
+        <v>8.172035219565997</v>
       </c>
       <c r="D6" t="n">
-        <v>60.02307598177835</v>
+        <v>9.753749847038982</v>
       </c>
       <c r="E6" t="n">
-        <v>12.9434067117825</v>
+        <v>2.103303590664656</v>
       </c>
       <c r="F6" t="n">
-        <v>16.94291744149149</v>
+        <v>2.753224084242368</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>20.78481928571612</v>
+        <v>3.37753313392887</v>
       </c>
       <c r="D7" t="n">
-        <v>23.30035375434621</v>
+        <v>3.786307485081259</v>
       </c>
       <c r="E7" t="n">
-        <v>12.9434067117825</v>
+        <v>2.103303590664656</v>
       </c>
       <c r="F7" t="n">
-        <v>16.94291744149149</v>
+        <v>2.753224084242368</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>40.43349961238673</v>
+        <v>6.570443687012844</v>
       </c>
       <c r="D8" t="n">
-        <v>53.40915976950182</v>
+        <v>8.678988462544046</v>
       </c>
       <c r="E8" t="n">
-        <v>12.9434067117825</v>
+        <v>2.103303590664656</v>
       </c>
       <c r="F8" t="n">
-        <v>16.94291744149149</v>
+        <v>2.753224084242368</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>44.68912896975426</v>
+        <v>7.261983457585068</v>
       </c>
       <c r="D9" t="n">
-        <v>24.6541813501606</v>
+        <v>4.006304469401098</v>
       </c>
       <c r="E9" t="n">
-        <v>12.9434067117825</v>
+        <v>2.103303590664656</v>
       </c>
       <c r="F9" t="n">
-        <v>16.94291744149149</v>
+        <v>2.753224084242368</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>10.98814657468535</v>
+        <v>1.78557381838637</v>
       </c>
       <c r="D10" t="n">
-        <v>9.621674731934023</v>
+        <v>1.563522143939279</v>
       </c>
       <c r="E10" t="n">
-        <v>12.9434067117825</v>
+        <v>2.103303590664656</v>
       </c>
       <c r="F10" t="n">
-        <v>16.94291744149149</v>
+        <v>2.753224084242368</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>18.1756716832541</v>
+        <v>2.953546648528791</v>
       </c>
       <c r="D11" t="n">
-        <v>8.323854920509635</v>
+        <v>1.352626424582816</v>
       </c>
       <c r="E11" t="n">
-        <v>12.9434067117825</v>
+        <v>2.103303590664656</v>
       </c>
       <c r="F11" t="n">
-        <v>16.94291744149149</v>
+        <v>2.753224084242368</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>24.12419652365467</v>
+        <v>3.920181935093884</v>
       </c>
       <c r="D12" t="n">
-        <v>15.47126227012271</v>
+        <v>2.514080118894941</v>
       </c>
       <c r="E12" t="n">
-        <v>12.9434067117825</v>
+        <v>2.103303590664656</v>
       </c>
       <c r="F12" t="n">
-        <v>16.94291744149149</v>
+        <v>2.753224084242368</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>20.58246062709636</v>
+        <v>3.344649851903159</v>
       </c>
       <c r="D13" t="n">
-        <v>11.76414643851222</v>
+        <v>1.911673796258236</v>
       </c>
       <c r="E13" t="n">
-        <v>12.9434067117825</v>
+        <v>2.103303590664656</v>
       </c>
       <c r="F13" t="n">
-        <v>16.94291744149149</v>
+        <v>2.753224084242368</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>26.45292298346496</v>
+        <v>4.298599984813056</v>
       </c>
       <c r="D14" t="n">
-        <v>17.13940919503626</v>
+        <v>2.785153994193393</v>
       </c>
       <c r="E14" t="n">
-        <v>12.9434067117825</v>
+        <v>2.103303590664656</v>
       </c>
       <c r="F14" t="n">
-        <v>16.94291744149149</v>
+        <v>2.753224084242368</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
